--- a/results/six_week_reports_20261028/report_02_弱配對補救.xlsx
+++ b/results/six_week_reports_20261028/report_02_弱配對補救.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">必要對照!$A$1:$H$20</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">結果比較!$A$1:$H$74</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">結果比較!$A$1:$H$78</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">設定與說明!$A$1:$H$28</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">必要對照!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">結果比較!$1:$3</definedName>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="98">
   <si>
     <t>第2次｜弱配對補救</t>
   </si>
@@ -57,15 +57,15 @@
     <t>本次成功／總數</t>
   </si>
   <si>
-    <t>差：後−前 pp</t>
+    <t>vs前一次 pp</t>
+  </si>
+  <si>
+    <t>vs論文 pp</t>
   </si>
   <si>
     <t>案例組成</t>
   </si>
   <si>
-    <t>批次</t>
-  </si>
-  <si>
     <t>Tongji／Plot1</t>
   </si>
   <si>
@@ -75,10 +75,7 @@
     <t>待補</t>
   </si>
   <si>
-    <t>10對×10seed</t>
-  </si>
-  <si>
-    <t>seed31–40</t>
+    <t>10對×10seed；31–40</t>
   </si>
   <si>
     <t>Tongji／Plot2</t>
@@ -117,7 +114,7 @@
     <t>150/150</t>
   </si>
   <si>
-    <t>15對×10seed</t>
+    <t>15對×10seed；31–40</t>
   </si>
   <si>
     <t>Tongji四Plot屬同一dataset，ETH屬另一dataset；兩者不混算誤差平均。前後均同配對與seed，失敗與缺輸出都保留。原論文門檻與分母未確認一致，100%只能作報告值參考。</t>
@@ -394,7 +391,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -409,13 +406,16 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -897,13 +897,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>752475</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -927,13 +927,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>752475</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1348,137 +1348,142 @@
       <c r="B8" s="5">
         <v>1</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="7">
         <f>(100/100-100/100)*100</f>
         <v>0.0</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="7">
+        <f>(100/100-B8)*100</f>
+        <v>0.0</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="45" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="5">
         <v>1</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="6">
+      <c r="E9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="7">
         <f>(34/100-34/100)*100</f>
         <v>0.0</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="7">
+        <f>(34/100-B9)*100</f>
+        <v>-65.99999999999999</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="45" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" s="5">
         <v>1</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="7">
         <f>(100/100-100/100)*100</f>
         <v>0.0</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="7">
+        <f>(100/100-B10)*100</f>
+        <v>0.0</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="45" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11" s="5">
         <v>1</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="6">
+      <c r="F11" s="7">
         <f>(95/100-70/100)*100</f>
         <v>25.0</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="7">
+        <f>(95/100-B11)*100</f>
+        <v>-5.000000000000004</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="45" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B12" s="5">
         <v>1</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F12" s="6">
+      <c r="F12" s="7">
         <f>(150/150-144/150)*100</f>
         <v>4.0000000000000036</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>30</v>
+      <c r="G12" s="7">
+        <f>(150/150-B12)*100</f>
+        <v>0.0</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="44" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1490,7 +1495,7 @@
     </row>
     <row r="17" spans="1:8" ht="28" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -1505,41 +1510,41 @@
         <v>5</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="45" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="8">
         <v>5.2558</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="8">
         <v>16.81264811104687</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="8">
         <v>17.4235311056</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="8">
         <v>17.42353110611136</v>
       </c>
       <c r="F19" s="5">
@@ -1551,23 +1556,23 @@
         <v>-2.315105427548872</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="45" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="7">
+        <v>17</v>
+      </c>
+      <c r="B20" s="8">
         <v>11.4808</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="8">
         <v>54.50497163856171</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="8">
         <v>50.90068114483</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="8">
         <v>50.90068114446461</v>
       </c>
       <c r="F20" s="5">
@@ -1579,23 +1584,23 @@
         <v>-3.4335482844805774</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="45" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="7">
+        <v>20</v>
+      </c>
+      <c r="B21" s="8">
         <v>4.8756</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="8">
         <v>5.376450884068796</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="8">
         <v>4.901756139286</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="8">
         <v>4.901756139380368</v>
       </c>
       <c r="F21" s="5">
@@ -1607,23 +1612,23 @@
         <v>-0.005364701653205442</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="45" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="7">
+        <v>21</v>
+      </c>
+      <c r="B22" s="8">
         <v>4.356</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="8">
         <v>123.234678935483</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="8">
         <v>252.1680517323086</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E22" s="8">
         <v>109.3731971735449</v>
       </c>
       <c r="F22" s="4" t="s">
@@ -1633,23 +1638,23 @@
         <v>15</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="45" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="7">
+        <v>25</v>
+      </c>
+      <c r="B23" s="8">
         <v>15.3427</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="8">
         <v>12.62093021050369</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="8">
         <v>9.095719413689656</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="8">
         <v>8.189515239489998</v>
       </c>
       <c r="F23" s="4" t="s">
@@ -1660,12 +1665,12 @@
         <v>0.4662272455636885</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="44" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -1677,7 +1682,7 @@
     </row>
     <row r="28" spans="1:8" ht="28" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -1692,16 +1697,16 @@
         <v>5</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="E29" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="45" customHeight="1">
@@ -1714,16 +1719,16 @@
       <c r="C30" s="5">
         <v>1</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="8">
         <v>17.4235311056</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E30" s="8">
         <v>17.42353110611136</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="45" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" s="5">
         <v>0.34</v>
@@ -1731,16 +1736,16 @@
       <c r="C31" s="5">
         <v>0.34</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="8">
         <v>50.90068114483</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E31" s="8">
         <v>50.90068114446461</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="45" customHeight="1">
       <c r="A32" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B32" s="5">
         <v>1</v>
@@ -1748,16 +1753,16 @@
       <c r="C32" s="5">
         <v>1</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32" s="8">
         <v>4.901756139286</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E32" s="8">
         <v>4.901756139380368</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="45" customHeight="1">
       <c r="A33" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B33" s="5">
         <v>0.7</v>
@@ -1765,16 +1770,16 @@
       <c r="C33" s="5">
         <v>0.95</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="8">
         <v>252.1680517323086</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E33" s="8">
         <v>109.3731971735449</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="45" customHeight="1">
       <c r="A34" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B34" s="5">
         <v>0.96</v>
@@ -1782,10 +1787,10 @@
       <c r="C34" s="5">
         <v>1</v>
       </c>
-      <c r="D34" s="7">
+      <c r="D34" s="8">
         <v>9.095719413689656</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E34" s="8">
         <v>8.189515239489998</v>
       </c>
     </row>
@@ -1864,7 +1869,7 @@
     </row>
     <row r="5" spans="1:8" ht="28" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -1876,77 +1881,77 @@
     </row>
     <row r="6" spans="1:8" ht="40" customHeight="1">
       <c r="A6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="45" customHeight="1">
       <c r="A7" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="45" customHeight="1">
       <c r="A8" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="45" customHeight="1">
       <c r="A9" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="45" customHeight="1">
       <c r="A10" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="46" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1958,7 +1963,7 @@
     </row>
     <row r="15" spans="1:8" ht="28" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -1973,88 +1978,88 @@
         <v>5</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="45" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="8">
         <v>20.718</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="8">
         <v>11.657</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="45" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="7">
+        <v>17</v>
+      </c>
+      <c r="B18" s="8">
         <v>30.699</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="8">
         <v>16.712</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="45" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="7">
+        <v>20</v>
+      </c>
+      <c r="B19" s="8">
         <v>4.5596</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="8">
         <v>8.3584</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="45" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="7">
+        <v>21</v>
+      </c>
+      <c r="B20" s="8">
         <v>19.522</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="8">
         <v>9.451599999999999</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="45" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="7">
+        <v>25</v>
+      </c>
+      <c r="B21" s="8">
         <v>3.0405</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="8">
         <v>8.699199999999999</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="28" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -2066,7 +2071,7 @@
     </row>
     <row r="25" spans="1:8" ht="38" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -2078,7 +2083,7 @@
     </row>
     <row r="26" spans="1:8" ht="38" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -2090,7 +2095,7 @@
     </row>
     <row r="27" spans="1:8" ht="38" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -2102,7 +2107,7 @@
     </row>
     <row r="28" spans="1:8" ht="52" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -2189,7 +2194,7 @@
     </row>
     <row r="5" spans="1:8" ht="28" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -2201,28 +2206,28 @@
     </row>
     <row r="6" spans="1:8" ht="40" customHeight="1">
       <c r="A6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="45" customHeight="1">
@@ -2238,10 +2243,10 @@
       <c r="D7" s="4">
         <v>100</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="8">
         <v>17.4235311056</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="8">
         <v>17.42353110611136</v>
       </c>
       <c r="G7" s="5">
@@ -2249,12 +2254,12 @@
         <v>-2.9348679083067623e-11</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="45" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="4">
         <v>0</v>
@@ -2265,10 +2270,10 @@
       <c r="D8" s="4">
         <v>34</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="8">
         <v>27.73532425420589</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="8">
         <v>27.73532425418735</v>
       </c>
       <c r="G8" s="5">
@@ -2276,12 +2281,12 @@
         <v>6.6828760414821e-13</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="45" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" s="4">
         <v>0</v>
@@ -2292,10 +2297,10 @@
       <c r="D9" s="4">
         <v>100</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="8">
         <v>4.901756139286</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="8">
         <v>4.901756139380368</v>
       </c>
       <c r="G9" s="5">
@@ -2303,12 +2308,12 @@
         <v>-1.9251929415136876e-11</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="45" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" s="4">
         <v>25</v>
@@ -2319,10 +2324,10 @@
       <c r="D10" s="4">
         <v>70</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="8">
         <v>7.479821179100001</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="8">
         <v>6.852978560495232</v>
       </c>
       <c r="G10" s="5">
@@ -2330,12 +2335,12 @@
         <v>0.08380449259352381</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="45" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11" s="4">
         <v>6</v>
@@ -2346,10 +2351,10 @@
       <c r="D11" s="4">
         <v>144</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="8">
         <v>9.067214102881945</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="8">
         <v>8.185600479232495</v>
       </c>
       <c r="G11" s="5">
@@ -2357,12 +2362,12 @@
         <v>0.0972309260205111</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="28" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -2377,155 +2382,155 @@
         <v>5</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="F15" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="45" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="8">
         <v>0.689562769167</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="8">
         <v>0.689562769163795</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="8">
         <v>15.2649956211</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="8">
         <v>15.26499562068555</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="8">
         <v>27.09175617</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="8">
         <v>9.366650740000001</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="45" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="7">
+        <v>17</v>
+      </c>
+      <c r="B17" s="8">
         <v>2.805820850935</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="8">
         <v>2.805820850931177</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="8">
         <v>31.61299917308</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="8">
         <v>31.61299917249332</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="8">
         <v>61.17425436</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="8">
         <v>17.11263271</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="45" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="7">
+        <v>20</v>
+      </c>
+      <c r="B18" s="8">
         <v>0.2756560181046</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="8">
         <v>0.2756560181035777</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="8">
         <v>4.498764577382</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="8">
         <v>4.498764577469081</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="8">
         <v>8.32219845</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="8">
         <v>4.2305661</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="45" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="7">
+        <v>21</v>
+      </c>
+      <c r="B19" s="8">
         <v>9.392364444529136</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="8">
         <v>4.011495700327153</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="8">
         <v>255.1452830486901</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="8">
         <v>110.7161576827211</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="8">
         <v>7.46682261</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="8">
         <v>6.28245099</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="45" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="7">
+        <v>25</v>
+      </c>
+      <c r="B20" s="8">
         <v>0.53536225928</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="8">
         <v>0.5085177018404022</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="8">
         <v>8.136594117781378</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="8">
         <v>7.295919161821776</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="8">
         <v>3.046398766666667</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="8">
         <v>3.351798066666666</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
